--- a/research/traditional_assets/database/data/denmark/denmark_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_insurance_prop_cas.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.05025</v>
+        <v>0.049865</v>
       </c>
       <c r="E2">
-        <v>-0.0381</v>
+        <v>-0.04975</v>
       </c>
       <c r="G2">
-        <v>0.1593047391801975</v>
+        <v>0.1805230487432584</v>
       </c>
       <c r="H2">
-        <v>0.1593047391801975</v>
+        <v>0.1805230487432584</v>
       </c>
       <c r="I2">
-        <v>0.1726512638460494</v>
+        <v>0.1135646687697161</v>
       </c>
       <c r="J2">
-        <v>0.1280415689584171</v>
+        <v>0.1008819184381086</v>
       </c>
       <c r="K2">
-        <v>516.2</v>
+        <v>403.4</v>
       </c>
       <c r="L2">
-        <v>0.1001377330307087</v>
+        <v>0.08210033580950443</v>
       </c>
       <c r="M2">
-        <v>927.15</v>
+        <v>795.6</v>
       </c>
       <c r="N2">
-        <v>0.04863329504146537</v>
+        <v>0.04532300330409024</v>
       </c>
       <c r="O2">
-        <v>1.796106160402944</v>
+        <v>1.97223599405057</v>
       </c>
       <c r="P2">
-        <v>907.4</v>
+        <v>514.3</v>
       </c>
       <c r="Q2">
-        <v>0.04759731642196589</v>
+        <v>0.02929816566024837</v>
       </c>
       <c r="R2">
-        <v>1.757845796203022</v>
+        <v>1.274913237481408</v>
       </c>
       <c r="S2">
-        <v>19.75</v>
+        <v>281.3</v>
       </c>
       <c r="T2">
-        <v>0.02130183896888314</v>
+        <v>0.3535696329813977</v>
       </c>
       <c r="U2">
-        <v>255.4</v>
+        <v>292.1</v>
       </c>
       <c r="V2">
-        <v>0.01339690832507173</v>
+        <v>0.01664008203258517</v>
       </c>
       <c r="W2">
-        <v>0.1563572977190527</v>
+        <v>0.09018197607650207</v>
       </c>
       <c r="X2">
-        <v>0.04878475267129381</v>
+        <v>0.08235163069858145</v>
       </c>
       <c r="Y2">
-        <v>0.1075725450477589</v>
+        <v>0.007830345377920614</v>
       </c>
       <c r="Z2">
-        <v>1.49166618438567</v>
+        <v>0.5627970906591835</v>
       </c>
       <c r="AA2">
-        <v>0.1613824088393191</v>
+        <v>0.1685523407463116</v>
       </c>
       <c r="AB2">
-        <v>0.04772708126696515</v>
+        <v>0.07924004173927182</v>
       </c>
       <c r="AC2">
-        <v>0.1136553275723539</v>
+        <v>0.08931229900703982</v>
       </c>
       <c r="AD2">
-        <v>951.6999999999999</v>
+        <v>1137.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>951.6999999999999</v>
+        <v>1137.1</v>
       </c>
       <c r="AG2">
-        <v>696.3</v>
+        <v>844.9999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.04754743752435576</v>
+        <v>0.06083644087292883</v>
       </c>
       <c r="AI2">
-        <v>0.1059091920765635</v>
+        <v>0.1301431792430155</v>
       </c>
       <c r="AJ2">
-        <v>0.0352371409485638</v>
+        <v>0.04592640904396977</v>
       </c>
       <c r="AK2">
-        <v>0.07975396879939523</v>
+        <v>0.1000568370198456</v>
       </c>
       <c r="AL2">
-        <v>29.29</v>
+        <v>21.89</v>
       </c>
       <c r="AM2">
-        <v>29.29</v>
+        <v>21.89</v>
       </c>
       <c r="AN2">
-        <v>0.9711224489795918</v>
+        <v>1.834032258064516</v>
       </c>
       <c r="AO2">
-        <v>30.3857972004097</v>
+        <v>25.49109182275011</v>
       </c>
       <c r="AP2">
-        <v>0.7105102040816326</v>
+        <v>1.362903225806452</v>
       </c>
       <c r="AQ2">
-        <v>30.3857972004097</v>
+        <v>25.49109182275011</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tryg A/S (CPSE:TRYG)</t>
+          <t>Alm. Brand A/S (CPSE:ALMB)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,121 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.07429999999999999</v>
+        <v>-0.00627</v>
       </c>
       <c r="E3">
-        <v>0.0118</v>
+        <v>-0.0984</v>
       </c>
       <c r="G3">
-        <v>0.1642516998141027</v>
+        <v>0.1120372165148285</v>
       </c>
       <c r="H3">
-        <v>0.1642516998141027</v>
+        <v>0.1120372165148285</v>
       </c>
       <c r="I3">
-        <v>0.1973566935750847</v>
+        <v>0.1540027137042063</v>
       </c>
       <c r="J3">
-        <v>0.1498726322544149</v>
+        <v>0.1540027137042063</v>
       </c>
       <c r="K3">
-        <v>440.3</v>
+        <v>69.3</v>
       </c>
       <c r="L3">
-        <v>0.1121240673304642</v>
+        <v>0.06716417910447761</v>
       </c>
       <c r="M3">
-        <v>566.3</v>
+        <v>61.6</v>
       </c>
       <c r="N3">
-        <v>0.03522971165510591</v>
+        <v>0.02474690663667042</v>
       </c>
       <c r="O3">
-        <v>1.286168521462639</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="P3">
-        <v>547.8</v>
+        <v>61.6</v>
       </c>
       <c r="Q3">
-        <v>0.03407882049208373</v>
+        <v>0.02474690663667042</v>
       </c>
       <c r="R3">
-        <v>1.24415171473995</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="S3">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.03266819706869151</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>222.2</v>
+        <v>72.5</v>
       </c>
       <c r="V3">
-        <v>0.0138231360228934</v>
+        <v>0.02912582355776957</v>
       </c>
       <c r="W3">
-        <v>0.2183702822000694</v>
+        <v>0.1359623307828134</v>
       </c>
       <c r="X3">
-        <v>0.04926516519897183</v>
+        <v>0.08306413799435873</v>
       </c>
       <c r="Y3">
-        <v>0.1691051170010976</v>
+        <v>0.05289819278845469</v>
       </c>
       <c r="Z3">
-        <v>1.536466077157837</v>
+        <v>1.943492183085327</v>
       </c>
       <c r="AA3">
-        <v>0.23027421535326</v>
+        <v>0.2993030702580524</v>
       </c>
       <c r="AB3">
-        <v>0.04762327520887887</v>
+        <v>0.07931205240760381</v>
       </c>
       <c r="AC3">
-        <v>0.1826509401443812</v>
+        <v>0.2199910178504486</v>
       </c>
       <c r="AD3">
-        <v>897.3</v>
+        <v>256.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>897.3</v>
+        <v>256.5</v>
       </c>
       <c r="AG3">
-        <v>675.0999999999999</v>
+        <v>184</v>
       </c>
       <c r="AH3">
-        <v>0.05287005503246562</v>
+        <v>0.09341880030593291</v>
       </c>
       <c r="AI3">
-        <v>0.1065436540448117</v>
+        <v>0.1250975419430355</v>
       </c>
       <c r="AJ3">
-        <v>0.04030544012991355</v>
+        <v>0.06883136316025737</v>
       </c>
       <c r="AK3">
-        <v>0.08233228044928471</v>
+        <v>0.09302795894635724</v>
       </c>
       <c r="AL3">
-        <v>26.8</v>
+        <v>3.69</v>
       </c>
       <c r="AM3">
-        <v>26.8</v>
+        <v>3.69</v>
       </c>
       <c r="AN3">
-        <v>1.122326454033771</v>
+        <v>1.784968684759917</v>
       </c>
       <c r="AO3">
-        <v>28.91791044776119</v>
+        <v>43.06233062330624</v>
       </c>
       <c r="AP3">
-        <v>0.8444027517198248</v>
+        <v>1.28044537230341</v>
       </c>
       <c r="AQ3">
-        <v>28.91791044776119</v>
+        <v>43.06233062330624</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alm. Brand A/S (CPSE:ALMB)</t>
+          <t>Tryg A/S (CPSE:TRYG)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,121 +856,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0262</v>
+        <v>0.106</v>
       </c>
       <c r="E4">
-        <v>-0.08800000000000001</v>
+        <v>-0.0011</v>
       </c>
       <c r="G4">
-        <v>0.143485342019544</v>
+        <v>0.1987273617229564</v>
       </c>
       <c r="H4">
-        <v>0.143485342019544</v>
+        <v>0.1987273617229564</v>
       </c>
       <c r="I4">
-        <v>0.09364820846905537</v>
+        <v>0.10281577659273</v>
       </c>
       <c r="J4">
-        <v>0.06778627206257352</v>
+        <v>0.07985111973593727</v>
       </c>
       <c r="K4">
-        <v>75.90000000000001</v>
+        <v>334.1</v>
       </c>
       <c r="L4">
-        <v>0.06180781758957656</v>
+        <v>0.08607053610531469</v>
       </c>
       <c r="M4">
-        <v>360.85</v>
+        <v>734</v>
       </c>
       <c r="N4">
-        <v>0.1207017661225582</v>
+        <v>0.04872285061866072</v>
       </c>
       <c r="O4">
-        <v>4.754281949934124</v>
+        <v>2.196947021849745</v>
       </c>
       <c r="P4">
-        <v>359.6</v>
+        <v>452.7</v>
       </c>
       <c r="Q4">
-        <v>0.1202836499866203</v>
+        <v>0.03005018320853911</v>
       </c>
       <c r="R4">
-        <v>4.737812911725955</v>
+        <v>1.354983537862915</v>
       </c>
       <c r="S4">
-        <v>1.25</v>
+        <v>281.3</v>
       </c>
       <c r="T4">
-        <v>0.003464043231259526</v>
+        <v>0.3832425068119891</v>
       </c>
       <c r="U4">
-        <v>33.2</v>
+        <v>219.6</v>
       </c>
       <c r="V4">
-        <v>0.01110516457051111</v>
+        <v>0.01457702724231321</v>
       </c>
       <c r="W4">
-        <v>0.09434431323803605</v>
+        <v>0.04440162137019071</v>
       </c>
       <c r="X4">
-        <v>0.04830434014361579</v>
+        <v>0.08163912340280416</v>
       </c>
       <c r="Y4">
-        <v>0.04603997309442026</v>
+        <v>-0.03723750203261345</v>
       </c>
       <c r="Z4">
-        <v>1.364444444444444</v>
+        <v>0.4734011415190986</v>
       </c>
       <c r="AA4">
-        <v>0.0924906023253781</v>
+        <v>0.03780161123457092</v>
       </c>
       <c r="AB4">
-        <v>0.04783088732505143</v>
+        <v>0.07916803107093984</v>
       </c>
       <c r="AC4">
-        <v>0.04465971500032668</v>
+        <v>-0.04136641983636891</v>
       </c>
       <c r="AD4">
-        <v>54.4</v>
+        <v>880.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>54.4</v>
+        <v>880.6</v>
       </c>
       <c r="AG4">
-        <v>21.2</v>
+        <v>661</v>
       </c>
       <c r="AH4">
-        <v>0.01787122207621551</v>
+        <v>0.05522595858366677</v>
       </c>
       <c r="AI4">
-        <v>0.09643680198546356</v>
+        <v>0.1316903198791667</v>
       </c>
       <c r="AJ4">
-        <v>0.007041317922146937</v>
+        <v>0.04203283775706165</v>
       </c>
       <c r="AK4">
-        <v>0.03993219061970239</v>
+        <v>0.1022064849318881</v>
       </c>
       <c r="AL4">
-        <v>2.49</v>
+        <v>18.2</v>
       </c>
       <c r="AM4">
-        <v>2.49</v>
+        <v>18.2</v>
       </c>
       <c r="AN4">
-        <v>0.3013850415512465</v>
+        <v>1.848834768003359</v>
       </c>
       <c r="AO4">
-        <v>46.18473895582329</v>
+        <v>21.92857142857143</v>
       </c>
       <c r="AP4">
-        <v>0.1174515235457063</v>
+        <v>1.387780810413605</v>
       </c>
       <c r="AQ4">
-        <v>46.18473895582329</v>
+        <v>21.92857142857143</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/denmark/denmark_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.049865</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="E2">
-        <v>-0.04975</v>
+        <v>0.0808</v>
       </c>
       <c r="G2">
-        <v>0.1805230487432584</v>
+        <v>0.1213118971061093</v>
       </c>
       <c r="H2">
-        <v>0.1805230487432584</v>
+        <v>0.1213118971061093</v>
       </c>
       <c r="I2">
-        <v>0.1135646687697161</v>
+        <v>0.1615176848874598</v>
       </c>
       <c r="J2">
-        <v>0.1008819184381086</v>
+        <v>0.1217146825788317</v>
       </c>
       <c r="K2">
-        <v>403.4</v>
+        <v>949.1999999999999</v>
       </c>
       <c r="L2">
-        <v>0.08210033580950443</v>
+        <v>0.1220836012861736</v>
       </c>
       <c r="M2">
-        <v>795.6</v>
+        <v>1513.85</v>
       </c>
       <c r="N2">
-        <v>0.04532300330409024</v>
+        <v>0.07412839095093526</v>
       </c>
       <c r="O2">
-        <v>1.97223599405057</v>
+        <v>1.594869363674673</v>
       </c>
       <c r="P2">
-        <v>514.3</v>
+        <v>1089</v>
       </c>
       <c r="Q2">
-        <v>0.02929816566024837</v>
+        <v>0.0533248457545784</v>
       </c>
       <c r="R2">
-        <v>1.274913237481408</v>
+        <v>1.147281921618205</v>
       </c>
       <c r="S2">
-        <v>281.3</v>
+        <v>424.85</v>
       </c>
       <c r="T2">
-        <v>0.3535696329813977</v>
+        <v>0.2806420715394524</v>
       </c>
       <c r="U2">
-        <v>292.1</v>
+        <v>534.8</v>
       </c>
       <c r="V2">
-        <v>0.01664008203258517</v>
+        <v>0.02618744491234943</v>
       </c>
       <c r="W2">
-        <v>0.09018197607650207</v>
+        <v>0.09288346939478488</v>
       </c>
       <c r="X2">
-        <v>0.08235163069858145</v>
+        <v>0.07121447076838926</v>
       </c>
       <c r="Y2">
-        <v>0.007830345377920614</v>
+        <v>0.02166899862639562</v>
       </c>
       <c r="Z2">
-        <v>0.5627970906591835</v>
+        <v>0.8280261560416623</v>
       </c>
       <c r="AA2">
-        <v>0.1685523407463116</v>
+        <v>0.09305792942026096</v>
       </c>
       <c r="AB2">
-        <v>0.07924004173927182</v>
+        <v>0.0683551331050492</v>
       </c>
       <c r="AC2">
-        <v>0.08931229900703982</v>
+        <v>0.02470279631521176</v>
       </c>
       <c r="AD2">
-        <v>1137.1</v>
+        <v>1620.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1137.1</v>
+        <v>1620.1</v>
       </c>
       <c r="AG2">
-        <v>844.9999999999999</v>
+        <v>1085.3</v>
       </c>
       <c r="AH2">
-        <v>0.06083644087292883</v>
+        <v>0.0735002563276639</v>
       </c>
       <c r="AI2">
-        <v>0.1301431792430155</v>
+        <v>0.1630404154254891</v>
       </c>
       <c r="AJ2">
-        <v>0.04592640904396977</v>
+        <v>0.05046193617980873</v>
       </c>
       <c r="AK2">
-        <v>0.1000568370198456</v>
+        <v>0.1154328866198681</v>
       </c>
       <c r="AL2">
-        <v>21.89</v>
+        <v>71.94</v>
       </c>
       <c r="AM2">
-        <v>21.89</v>
+        <v>71.94</v>
       </c>
       <c r="AN2">
-        <v>1.834032258064516</v>
+        <v>1.10700375811411</v>
       </c>
       <c r="AO2">
-        <v>25.49109182275011</v>
+        <v>17.45621351125938</v>
       </c>
       <c r="AP2">
-        <v>1.362903225806452</v>
+        <v>0.7415784079262044</v>
       </c>
       <c r="AQ2">
-        <v>25.49109182275011</v>
+        <v>17.45621351125938</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alm. Brand A/S (CPSE:ALMB)</t>
+          <t>Topdanmark A/S (CPSE:TOP)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.00627</v>
+        <v>-0.164</v>
       </c>
       <c r="E3">
-        <v>-0.0984</v>
+        <v>0.0808</v>
       </c>
       <c r="G3">
-        <v>0.1120372165148285</v>
+        <v>0.1564973614775726</v>
       </c>
       <c r="H3">
-        <v>0.1120372165148285</v>
+        <v>0.1564973614775726</v>
       </c>
       <c r="I3">
-        <v>0.1540027137042063</v>
+        <v>0.2076187335092348</v>
       </c>
       <c r="J3">
-        <v>0.1540027137042063</v>
+        <v>0.1541140290660412</v>
       </c>
       <c r="K3">
-        <v>69.3</v>
+        <v>303.5</v>
       </c>
       <c r="L3">
-        <v>0.06716417910447761</v>
+        <v>0.2502473614775726</v>
       </c>
       <c r="M3">
-        <v>61.6</v>
+        <v>389.8</v>
       </c>
       <c r="N3">
-        <v>0.02474690663667042</v>
+        <v>0.0918624655339005</v>
       </c>
       <c r="O3">
-        <v>0.888888888888889</v>
+        <v>1.284349258649094</v>
       </c>
       <c r="P3">
-        <v>61.6</v>
+        <v>389.8</v>
       </c>
       <c r="Q3">
-        <v>0.02474690663667042</v>
+        <v>0.0918624655339005</v>
       </c>
       <c r="R3">
-        <v>0.888888888888889</v>
+        <v>1.284349258649094</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>72.5</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="V3">
-        <v>0.02912582355776957</v>
+        <v>0.0183583531685245</v>
       </c>
       <c r="W3">
-        <v>0.1359623307828134</v>
+        <v>0.4559110710530269</v>
       </c>
       <c r="X3">
-        <v>0.08306413799435873</v>
+        <v>0.07016300248496427</v>
       </c>
       <c r="Y3">
-        <v>0.05289819278845469</v>
+        <v>0.3857480685680626</v>
       </c>
       <c r="Z3">
-        <v>1.943492183085327</v>
+        <v>1.283793796972584</v>
       </c>
       <c r="AA3">
-        <v>0.2993030702580524</v>
+        <v>0.1978506345414361</v>
       </c>
       <c r="AB3">
-        <v>0.07931205240760381</v>
+        <v>0.06876109489852245</v>
       </c>
       <c r="AC3">
-        <v>0.2199910178504486</v>
+        <v>0.1290895396429137</v>
       </c>
       <c r="AD3">
-        <v>256.5</v>
+        <v>176.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>256.5</v>
+        <v>176.9</v>
       </c>
       <c r="AG3">
-        <v>184</v>
+        <v>99</v>
       </c>
       <c r="AH3">
-        <v>0.09341880030593291</v>
+        <v>0.04002081353784897</v>
       </c>
       <c r="AI3">
-        <v>0.1250975419430355</v>
+        <v>0.2139315515781836</v>
       </c>
       <c r="AJ3">
-        <v>0.06883136316025737</v>
+        <v>0.02279897750040301</v>
       </c>
       <c r="AK3">
-        <v>0.09302795894635724</v>
+        <v>0.1321762349799733</v>
       </c>
       <c r="AL3">
-        <v>3.69</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AM3">
-        <v>3.69</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AN3">
-        <v>1.784968684759917</v>
+        <v>0.6806464024624856</v>
       </c>
       <c r="AO3">
-        <v>43.06233062330624</v>
+        <v>26.12033195020747</v>
       </c>
       <c r="AP3">
-        <v>1.28044537230341</v>
+        <v>0.3809157368218546</v>
       </c>
       <c r="AQ3">
-        <v>43.06233062330624</v>
+        <v>26.12033195020747</v>
       </c>
     </row>
     <row r="4">
@@ -856,121 +856,255 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.106</v>
+        <v>0.149</v>
       </c>
       <c r="E4">
-        <v>-0.0011</v>
+        <v>0.121</v>
       </c>
       <c r="G4">
-        <v>0.1987273617229564</v>
+        <v>0.137470284449545</v>
       </c>
       <c r="H4">
-        <v>0.1987273617229564</v>
+        <v>0.137470284449545</v>
       </c>
       <c r="I4">
-        <v>0.10281577659273</v>
+        <v>0.1627387490777933</v>
       </c>
       <c r="J4">
-        <v>0.07985111973593727</v>
+        <v>0.1233347489848987</v>
       </c>
       <c r="K4">
-        <v>334.1</v>
+        <v>539.3</v>
       </c>
       <c r="L4">
-        <v>0.08607053610531469</v>
+        <v>0.1105213542093614</v>
       </c>
       <c r="M4">
-        <v>734</v>
+        <v>1055</v>
       </c>
       <c r="N4">
-        <v>0.04872285061866072</v>
+        <v>0.07839960763039973</v>
       </c>
       <c r="O4">
-        <v>2.196947021849745</v>
+        <v>1.95623956981272</v>
       </c>
       <c r="P4">
-        <v>452.7</v>
+        <v>633.7</v>
       </c>
       <c r="Q4">
-        <v>0.03005018320853911</v>
+        <v>0.04709178327524579</v>
       </c>
       <c r="R4">
-        <v>1.354983537862915</v>
+        <v>1.17504172074912</v>
       </c>
       <c r="S4">
-        <v>281.3</v>
+        <v>421.3</v>
       </c>
       <c r="T4">
-        <v>0.3832425068119891</v>
+        <v>0.3993364928909952</v>
       </c>
       <c r="U4">
-        <v>219.6</v>
+        <v>422.7</v>
       </c>
       <c r="V4">
-        <v>0.01457702724231321</v>
+        <v>0.03141186174916584</v>
       </c>
       <c r="W4">
-        <v>0.04440162137019071</v>
+        <v>0.09288346939478488</v>
       </c>
       <c r="X4">
-        <v>0.08163912340280416</v>
+        <v>0.07121447076838926</v>
       </c>
       <c r="Y4">
-        <v>-0.03723750203261345</v>
+        <v>0.02166899862639562</v>
       </c>
       <c r="Z4">
-        <v>0.4734011415190986</v>
+        <v>0.7545150915388422</v>
       </c>
       <c r="AA4">
-        <v>0.03780161123457092</v>
+        <v>0.09305792942026096</v>
       </c>
       <c r="AB4">
-        <v>0.07916803107093984</v>
+        <v>0.0683551331050492</v>
       </c>
       <c r="AC4">
-        <v>-0.04136641983636891</v>
+        <v>0.02470279631521176</v>
       </c>
       <c r="AD4">
-        <v>880.6</v>
+        <v>1158.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>880.6</v>
+        <v>1158.2</v>
       </c>
       <c r="AG4">
-        <v>661</v>
+        <v>735.5</v>
       </c>
       <c r="AH4">
-        <v>0.05522595858366677</v>
+        <v>0.07924789085111769</v>
       </c>
       <c r="AI4">
-        <v>0.1316903198791667</v>
+        <v>0.1688116719380839</v>
       </c>
       <c r="AJ4">
-        <v>0.04203283775706165</v>
+        <v>0.05182424148475923</v>
       </c>
       <c r="AK4">
-        <v>0.1022064849318881</v>
+        <v>0.1142400049703333</v>
       </c>
       <c r="AL4">
-        <v>18.2</v>
+        <v>41.3</v>
       </c>
       <c r="AM4">
-        <v>18.2</v>
+        <v>41.3</v>
       </c>
       <c r="AN4">
-        <v>1.848834768003359</v>
+        <v>1.249541482360557</v>
       </c>
       <c r="AO4">
-        <v>21.92857142857143</v>
+        <v>19.22760290556901</v>
       </c>
       <c r="AP4">
-        <v>1.387780810413605</v>
+        <v>0.7935052324954148</v>
       </c>
       <c r="AQ4">
-        <v>21.92857142857143</v>
+        <v>19.22760290556901</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Alm. Brand A/S (CPSE:ALMB)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.06660000000000001</v>
+      </c>
+      <c r="E5">
+        <v>0.0408</v>
+      </c>
+      <c r="G5">
+        <v>0.04909069297515749</v>
+      </c>
+      <c r="H5">
+        <v>0.04909069297515749</v>
+      </c>
+      <c r="I5">
+        <v>0.1247474147153215</v>
+      </c>
+      <c r="J5">
+        <v>0.09487580361479779</v>
+      </c>
+      <c r="K5">
+        <v>106.4</v>
+      </c>
+      <c r="L5">
+        <v>0.06323546891715204</v>
+      </c>
+      <c r="M5">
+        <v>69.05</v>
+      </c>
+      <c r="N5">
+        <v>0.02536737692872888</v>
+      </c>
+      <c r="O5">
+        <v>0.6489661654135338</v>
+      </c>
+      <c r="P5">
+        <v>65.5</v>
+      </c>
+      <c r="Q5">
+        <v>0.02406318883174137</v>
+      </c>
+      <c r="R5">
+        <v>0.6156015037593985</v>
+      </c>
+      <c r="S5">
+        <v>3.549999999999997</v>
+      </c>
+      <c r="T5">
+        <v>0.05141202027516289</v>
+      </c>
+      <c r="U5">
+        <v>34.2</v>
+      </c>
+      <c r="V5">
+        <v>0.01256429096252755</v>
+      </c>
+      <c r="W5">
+        <v>0.05931211327275768</v>
+      </c>
+      <c r="X5">
+        <v>0.07165595541952557</v>
+      </c>
+      <c r="Y5">
+        <v>-0.0123438421467679</v>
+      </c>
+      <c r="Z5">
+        <v>0.8507002376257646</v>
+      </c>
+      <c r="AA5">
+        <v>0.08071086868004386</v>
+      </c>
+      <c r="AB5">
+        <v>0.06819440291052498</v>
+      </c>
+      <c r="AC5">
+        <v>0.01251646576951888</v>
+      </c>
+      <c r="AD5">
+        <v>285</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>285</v>
+      </c>
+      <c r="AG5">
+        <v>250.8</v>
+      </c>
+      <c r="AH5">
+        <v>0.09477884935151314</v>
+      </c>
+      <c r="AI5">
+        <v>0.1267229879946643</v>
+      </c>
+      <c r="AJ5">
+        <v>0.08436490850376749</v>
+      </c>
+      <c r="AK5">
+        <v>0.1132382156402384</v>
+      </c>
+      <c r="AL5">
+        <v>21</v>
+      </c>
+      <c r="AM5">
+        <v>21</v>
+      </c>
+      <c r="AN5">
+        <v>1.029996385977593</v>
+      </c>
+      <c r="AO5">
+        <v>9.995238095238095</v>
+      </c>
+      <c r="AP5">
+        <v>0.906396819660282</v>
+      </c>
+      <c r="AQ5">
+        <v>9.995238095238095</v>
       </c>
     </row>
   </sheetData>
